--- a/samples/ss_plbratu_ingest.xlsx
+++ b/samples/ss_plbratu_ingest.xlsx
@@ -572,7 +572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T42"/>
+  <dimension ref="A1:U42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -613,65 +613,70 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Bus 150 kV</t>
+          <t>Bus HV</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>Bus LV</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>Jumlah Trafo</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Jumlah Kapasitor</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Catatan Simbol</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Jumlah Sirkit Bay</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Status Operasi</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Role</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Status Kerawanan</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>No Kerawanan</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Wilayah</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Sudut Pandang</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Latitude</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Longitude</t>
         </is>
@@ -710,24 +715,25 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr">
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>Jawa Barat</t>
-        </is>
-      </c>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
+        <is>
+          <t>Jawa Barat</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>CIBINONG</t>
         </is>
@@ -767,37 +773,42 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>CIBNG7</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>CIBNG</t>
         </is>
       </c>
-      <c r="I3" t="n">
-        <v>2</v>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
+      <c r="J3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
         <is>
           <t>2 IBT (unit 1,2)</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr">
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>Jawa Barat</t>
-        </is>
-      </c>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
+        <is>
+          <t>Jawa Barat</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>CIBINONG</t>
         </is>
@@ -836,24 +847,25 @@
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr">
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>Jawa Barat</t>
-        </is>
-      </c>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
+        <is>
+          <t>Jawa Barat</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>CIBINONG</t>
         </is>
@@ -893,37 +905,42 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
+          <t>DEPOK7</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>DEPOK</t>
         </is>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>1</v>
       </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
         <is>
           <t>1 IBT (unit 2)</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr">
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>Jawa Barat</t>
-        </is>
-      </c>
+      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
+        <is>
+          <t>Jawa Barat</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>CIBINONG</t>
         </is>
@@ -960,34 +977,35 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
         <is>
           <t>bus section + kopel</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr">
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>Jawa Barat</t>
-        </is>
-      </c>
       <c r="R6" t="inlineStr">
+        <is>
+          <t>Jawa Barat</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>CIBINONG</t>
         </is>
@@ -1026,24 +1044,25 @@
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr">
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>Jawa Barat</t>
-        </is>
-      </c>
+      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
+        <is>
+          <t>Jawa Barat</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
         <is>
           <t>CIBINONG</t>
         </is>
@@ -1082,24 +1101,25 @@
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr">
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>Jawa Barat</t>
-        </is>
-      </c>
+      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
+        <is>
+          <t>Jawa Barat</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>CIBINONG</t>
         </is>
@@ -1138,24 +1158,25 @@
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr">
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>Jawa Barat</t>
-        </is>
-      </c>
+      <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
+        <is>
+          <t>Jawa Barat</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>CIBINONG</t>
         </is>
@@ -1192,30 +1213,31 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
         <is>
           <t>KTT ITP 220 MVA</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr">
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>Jawa Barat</t>
-        </is>
-      </c>
+      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
+        <is>
+          <t>Jawa Barat</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
         <is>
           <t>CIBINONG</t>
         </is>
@@ -1254,24 +1276,25 @@
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr">
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>Jawa Barat</t>
-        </is>
-      </c>
+      <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
+        <is>
+          <t>Jawa Barat</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
         <is>
           <t>CIBINONG</t>
         </is>
@@ -1311,37 +1334,42 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
+          <t>CIBNG</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
           <t>CIBN4</t>
         </is>
       </c>
-      <c r="I12" t="n">
-        <v>2</v>
-      </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
+      <c r="J12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
         <is>
           <t>2 IBT 150/70 kV</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr">
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>Jawa Barat</t>
-        </is>
-      </c>
+      <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
+        <is>
+          <t>Jawa Barat</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
         <is>
           <t>CIBINONG</t>
         </is>
@@ -1380,24 +1408,25 @@
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr">
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>Jawa Barat</t>
-        </is>
-      </c>
+      <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
+        <is>
+          <t>Jawa Barat</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
         <is>
           <t>CIBINONG</t>
         </is>
@@ -1434,30 +1463,31 @@
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
         <is>
           <t>KTT Aspek 40 MVA</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr">
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>Jawa Barat</t>
-        </is>
-      </c>
+      <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
+        <is>
+          <t>Jawa Barat</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
         <is>
           <t>CIBINONG</t>
         </is>
@@ -1497,37 +1527,42 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
+          <t>SMNRU</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
           <t>SMNRU4</t>
         </is>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>1</v>
       </c>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
         <is>
           <t>IBT 150/70 kV</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr">
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>Jawa Barat</t>
-        </is>
-      </c>
+      <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
+        <is>
+          <t>Jawa Barat</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
         <is>
           <t>CIBINONG</t>
         </is>
@@ -1566,24 +1601,25 @@
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr">
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>Jawa Barat</t>
-        </is>
-      </c>
+      <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
+        <is>
+          <t>Jawa Barat</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
         <is>
           <t>CIBINONG</t>
         </is>
@@ -1620,30 +1656,31 @@
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
         <is>
           <t>KTT Sucofindo 40 MVA</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr">
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>Jawa Barat</t>
-        </is>
-      </c>
+      <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
+        <is>
+          <t>Jawa Barat</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
         <is>
           <t>CIBINONG</t>
         </is>
@@ -1680,30 +1717,31 @@
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
         <is>
           <t>aset milik KTT</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr">
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>Jawa Barat</t>
-        </is>
-      </c>
+      <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
+        <is>
+          <t>Jawa Barat</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
         <is>
           <t>CIBINONG</t>
         </is>
@@ -1742,24 +1780,25 @@
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr">
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>Jawa Barat</t>
-        </is>
-      </c>
+      <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
+        <is>
+          <t>Jawa Barat</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
         <is>
           <t>SALAK</t>
         </is>
@@ -1796,34 +1835,35 @@
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
         <is>
           <t>T/L bay single phi arah Bogor Baru &amp; Cibadak Baru</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr">
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="Q20" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>Jawa Barat</t>
-        </is>
-      </c>
       <c r="R20" t="inlineStr">
+        <is>
+          <t>Jawa Barat</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
         <is>
           <t>SALAK</t>
         </is>
@@ -1862,28 +1902,29 @@
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr">
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="Q21" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>Jawa Barat</t>
-        </is>
-      </c>
       <c r="R21" t="inlineStr">
+        <is>
+          <t>Jawa Barat</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
         <is>
           <t>SALAK</t>
         </is>
@@ -1922,28 +1963,29 @@
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr">
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="Q22" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>Jawa Barat</t>
-        </is>
-      </c>
       <c r="R22" t="inlineStr">
+        <is>
+          <t>Jawa Barat</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
         <is>
           <t>SALAK</t>
         </is>
@@ -1980,30 +2022,31 @@
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
         <is>
           <t>KTT Cemindo 70 MVA</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr">
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>Jawa Barat</t>
-        </is>
-      </c>
+      <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
+        <is>
+          <t>Jawa Barat</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
         <is>
           <t>SALAK</t>
         </is>
@@ -2042,28 +2085,29 @@
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr">
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
+      <c r="Q24" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>Jawa Barat</t>
-        </is>
-      </c>
       <c r="R24" t="inlineStr">
+        <is>
+          <t>Jawa Barat</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
         <is>
           <t>SALAK</t>
         </is>
@@ -2102,24 +2146,25 @@
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr">
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>Jawa Barat</t>
-        </is>
-      </c>
+      <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
+        <is>
+          <t>Jawa Barat</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
         <is>
           <t>SALAK</t>
         </is>
@@ -2158,28 +2203,29 @@
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr">
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="Q26" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>Jawa Barat</t>
-        </is>
-      </c>
       <c r="R26" t="inlineStr">
+        <is>
+          <t>Jawa Barat</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
         <is>
           <t>SALAK</t>
         </is>
@@ -2218,24 +2264,25 @@
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr">
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>Jawa Barat</t>
-        </is>
-      </c>
+      <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
+        <is>
+          <t>Jawa Barat</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
         <is>
           <t>SALAK</t>
         </is>
@@ -2274,24 +2321,25 @@
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr">
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>Jawa Barat</t>
-        </is>
-      </c>
+      <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
+        <is>
+          <t>Jawa Barat</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
         <is>
           <t>SALAK</t>
         </is>
@@ -2331,37 +2379,42 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
+          <t>CBDRU</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
           <t>CBDK4</t>
         </is>
       </c>
-      <c r="I29" t="n">
+      <c r="J29" t="n">
         <v>1</v>
       </c>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
         <is>
           <t>IBT 150/70 kV</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr">
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>Jawa Barat</t>
-        </is>
-      </c>
+      <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
+        <is>
+          <t>Jawa Barat</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
         <is>
           <t>SALAK</t>
         </is>
@@ -2400,24 +2453,25 @@
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr">
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>Jawa Barat</t>
-        </is>
-      </c>
+      <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
+        <is>
+          <t>Jawa Barat</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
         <is>
           <t>SALAK</t>
         </is>
@@ -2456,24 +2510,25 @@
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr">
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>Jawa Barat</t>
-        </is>
-      </c>
+      <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
+        <is>
+          <t>Jawa Barat</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
         <is>
           <t>SALAK</t>
         </is>
@@ -2512,24 +2567,25 @@
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr">
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>Jawa Barat</t>
-        </is>
-      </c>
+      <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
+        <is>
+          <t>Jawa Barat</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
         <is>
           <t>SALAK</t>
         </is>
@@ -2566,34 +2622,35 @@
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
         <is>
           <t>GI simpul; trafo &gt;70%</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr">
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr">
+      <c r="Q33" t="inlineStr">
         <is>
           <t>1;6</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>Jawa Barat</t>
-        </is>
-      </c>
       <c r="R33" t="inlineStr">
+        <is>
+          <t>Jawa Barat</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
         <is>
           <t>CIBINONG;SALAK</t>
         </is>
@@ -2632,28 +2689,29 @@
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr">
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr">
+      <c r="Q34" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>Jawa Barat</t>
-        </is>
-      </c>
       <c r="R34" t="inlineStr">
+        <is>
+          <t>Jawa Barat</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
         <is>
           <t>CIBINONG;SALAK</t>
         </is>
@@ -2692,28 +2750,29 @@
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr">
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr">
+      <c r="Q35" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>Jawa Barat</t>
-        </is>
-      </c>
       <c r="R35" t="inlineStr">
+        <is>
+          <t>Jawa Barat</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
         <is>
           <t>CIBINONG;SALAK</t>
         </is>
@@ -2752,24 +2811,25 @@
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr">
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>Jawa Barat</t>
-        </is>
-      </c>
+      <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr">
+        <is>
+          <t>Jawa Barat</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
         <is>
           <t>SALAK</t>
         </is>
@@ -2808,24 +2868,25 @@
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr">
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>Jawa Barat</t>
-        </is>
-      </c>
+      <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr">
+        <is>
+          <t>Jawa Barat</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
         <is>
           <t>SALAK</t>
         </is>
@@ -2864,24 +2925,25 @@
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr">
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>Jawa Barat</t>
-        </is>
-      </c>
+      <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr">
+        <is>
+          <t>Jawa Barat</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
         <is>
           <t>SALAK</t>
         </is>
@@ -2920,24 +2982,25 @@
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr">
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>Jawa Barat</t>
-        </is>
-      </c>
+      <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr">
+        <is>
+          <t>Jawa Barat</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
         <is>
           <t>SALAK</t>
         </is>
@@ -2976,24 +3039,25 @@
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr">
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>Jawa Barat</t>
-        </is>
-      </c>
+      <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr">
+        <is>
+          <t>Jawa Barat</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
         <is>
           <t>SALAK</t>
         </is>
@@ -3030,34 +3094,35 @@
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
         <is>
           <t>UP2B 2 (JABAR): CNJUR : - / CGRLG : Trf 9,10</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
+      <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr">
         <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
           <t>SOURCE_BOUNDARY</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr">
+      <c r="P41" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>Jawa Barat</t>
-        </is>
-      </c>
+      <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr">
+        <is>
+          <t>Jawa Barat</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
         <is>
           <t>SALAK</t>
         </is>
@@ -3094,34 +3159,35 @@
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
         <is>
           <t>UP2B 2 (JABAR): LGDAR Trf 1,2,3,4</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
+      <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
           <t>SOURCE_BOUNDARY</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr">
+      <c r="P42" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="inlineStr">
-        <is>
-          <t>Jawa Barat</t>
-        </is>
-      </c>
+      <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr">
+        <is>
+          <t>Jawa Barat</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
         <is>
           <t>SALAK</t>
         </is>

--- a/samples/ss_plbratu_ingest.xlsx
+++ b/samples/ss_plbratu_ingest.xlsx
@@ -768,7 +768,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1,2</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">

--- a/samples/ss_plbratu_ingest.xlsx
+++ b/samples/ss_plbratu_ingest.xlsx
@@ -5294,7 +5294,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5320,25 +5320,30 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Jenis</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Tegangan</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Jumlah Sirkit</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Status Operasi</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>No Kerawanan</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Sudut Pandang</t>
         </is>
@@ -5363,21 +5368,22 @@
           <t>CIBNG</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
         <is>
           <t>150 kV</t>
         </is>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>1</v>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr">
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
         <is>
           <t>CIBINONG</t>
         </is>
@@ -5445,12 +5451,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>BELUM_DITETAPKAN</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[N-1] GI 150 kV Bogor Baru merupakan GI Simpul yang apabila terjadi gangguan Busbar dapat mengakibatlkan terpisahnya IBT Cibinong, IBT Depok dan Komplek Pembangkitan Salak dan Pelabuhan Ratu sehingga berdampak sebagian beban padam pada Subsistem Pelabuhan Ratu - Salak - Cibinong 1,2-Depok 2</t>
+          <t>[BELUM_DITETAPKAN] GI 150 kV Bogor Baru merupakan GI Simpul yang apabila terjadi gangguan Busbar dapat mengakibatlkan terpisahnya IBT Cibinong, IBT Depok dan Komplek Pembangkitan Salak dan Pelabuhan Ratu sehingga berdampak sebagian beban padam pada Subsistem Pelabuhan Ratu - Salak - Cibinong 1,2-Depok 2</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -5515,12 +5521,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>BELUM_DITETAPKAN</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[N-1] SUTT 150 kV Bogor Baru- Sentul terjadi Derating dari CCC 1.350 A menjadi 1.000 A karena permasalahan andongan di T.14-T.15</t>
+          <t>[BELUM_DITETAPKAN] SUTT 150 kV Bogor Baru- Sentul terjadi Derating dari CCC 1.350 A menjadi 1.000 A karena permasalahan andongan di T.14-T.15</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -5550,12 +5556,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>BELUM_DITETAPKAN</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>[N-1] SUTT 150 kV Bogor Baru- Cianjur dan Bogor Baru- Katulampa-Cianjur memilikiratingarus kecil yaitu sebesar 600 A (Dove 327,94 mm2)</t>
+          <t>[BELUM_DITETAPKAN] SUTT 150 kV Bogor Baru- Cianjur dan Bogor Baru- Katulampa-Cianjur memilikiratingarus kecil yaitu sebesar 600 A (Dove 327,94 mm2)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -5585,12 +5591,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>BELUM_DITETAPKAN</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>[N-1] Hubung singkat di GI 150 kV Cibinong sudah diatas nilai breaking capacity PMT terkecil yang terpasang (40 kA) saat SUTT Cimanggis-Depok Baru II beroperasi (COD 2023)</t>
+          <t>[BELUM_DITETAPKAN] Hubung singkat di GI 150 kV Cibinong sudah diatas nilai breaking capacity PMT terkecil yang terpasang (40 kA) saat SUTT Cimanggis-Depok Baru II beroperasi (COD 2023)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -5655,12 +5661,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>N-2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>[N-1] Terjadi ketidakstabilan kit pratu saat terjadi N- 2SUTT 150 kVPratu - CibadakBaru</t>
+          <t>[N-2] Terjadi ketidakstabilan kit pratu saat terjadi N- 2SUTT 150 kVPratu - CibadakBaru</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -5690,12 +5696,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>BELUM_DITETAPKAN</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>[N-1] SUTT 150 kV Pelabuhan Ratu-Lembur Situ- Semen jawa memiliki rating arus kecil (1600 A)</t>
+          <t>[BELUM_DITETAPKAN] SUTT 150 kV Pelabuhan Ratu-Lembur Situ- Semen jawa memiliki rating arus kecil (1600 A)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">

--- a/samples/ss_plbratu_ingest.xlsx
+++ b/samples/ss_plbratu_ingest.xlsx
@@ -572,7 +572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U42"/>
+  <dimension ref="A1:U43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -745,7 +745,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>IBT 1,2 Cibinong 500/150 kV</t>
+          <t>IBT 1 Cibinong 500/150 kV</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -782,14 +782,10 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>2 IBT (unit 1,2)</t>
-        </is>
-      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
@@ -820,31 +816,45 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>GITET Depok</t>
+          <t>IBT 2 Cibinong 500/150 kV</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DEPOK7</t>
+          <t>IBT 2 CIBNG7</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Busbar GITET</t>
+          <t>IBT 3-Winding</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>500 kV</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>500/150 kV</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>CIBNG7</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>CIBNG</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
@@ -877,51 +887,33 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>IBT 2 Depok 500/150 kV</t>
+          <t>GITET Depok</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>IBT 2 DEPOK7</t>
+          <t>DEPOK7</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>IBT 3-Winding</t>
+          <t>Busbar GITET</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>500/150 kV</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>DEPOK7</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>DEPOK</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
+          <t>500 kV</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>1 IBT (unit 2)</t>
-        </is>
-      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
@@ -952,35 +944,49 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Cibinong (bus 150 kV)</t>
+          <t>IBT 2 Depok 500/150 kV</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CIBNG</t>
+          <t>IBT 2 DEPOK7</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Busbar GI</t>
+          <t>IBT 3-Winding</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>500/150 kV</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>DEPOK7</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>DEPOK</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>bus section + kopel</t>
+          <t>1 IBT (unit 2)</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
@@ -992,14 +998,10 @@
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -1017,12 +1019,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Depok (bus 150 kV)</t>
+          <t>Cibinong (bus 150 kV)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DEPOK</t>
+          <t>CIBNG</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1043,7 +1045,11 @@
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>bus section + kopel</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
@@ -1053,10 +1059,14 @@
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="R7" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -1074,12 +1084,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Semen Baru</t>
+          <t>Depok (bus 150 kV)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>SMNRU</t>
+          <t>DEPOK</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1088,7 +1098,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1131,17 +1141,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Cimanggis (GIS)</t>
+          <t>Semen Baru</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CMGIS</t>
+          <t>SMNRU</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Busbar GIS</t>
+          <t>Busbar GI</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1188,21 +1198,21 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ITP</t>
+          <t>Cimanggis (GIS)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ITP</t>
+          <t>CMGIS</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Busbar GI</t>
+          <t>Busbar GIS</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1214,11 +1224,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>KTT ITP 220 MVA</t>
-        </is>
-      </c>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
@@ -1249,12 +1255,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Depok Baru</t>
+          <t>ITP</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>DPBRU</t>
+          <t>ITP</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1263,7 +1269,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1275,7 +1281,11 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>KTT ITP 220 MVA</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
@@ -1306,17 +1316,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>IBT 150/70 kV Cibinong</t>
+          <t>Depok Baru</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>IBT 1 CIBNG</t>
+          <t>DPBRU</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>IBT 3-Winding</t>
+          <t>Busbar GI</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1324,33 +1334,15 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>150/70 kV</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>CIBNG</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>CIBN4</t>
-        </is>
-      </c>
-      <c r="J12" t="n">
-        <v>2</v>
-      </c>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>2 IBT 150/70 kV</t>
-        </is>
-      </c>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
@@ -1381,17 +1373,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Cibinong (bus 70 kV)</t>
+          <t>IBT 150/70 kV Cibinong</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CIBN4</t>
+          <t>IBT 1 CIBNG</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Busbar GI</t>
+          <t>IBT 3-Winding</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1399,15 +1391,33 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>70 kV</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+          <t>150/70 kV</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>CIBNG</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>CIBN4</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>2</v>
+      </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>2 IBT 150/70 kV</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
@@ -1438,12 +1448,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Cileungsi</t>
+          <t>Cibinong (bus 70 kV)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CLGSI</t>
+          <t>CIBN4</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1452,7 +1462,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1464,11 +1474,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>KTT Aspek 40 MVA</t>
-        </is>
-      </c>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
@@ -1499,17 +1505,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>IBT 150/70 kV Semen Baru</t>
+          <t>Cileungsi</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>IBT 1 SMNRU</t>
+          <t>CLGSI</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>IBT 3-Winding</t>
+          <t>Busbar GI</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -1517,31 +1523,17 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>150/70 kV</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>SMNRU</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>SMNRU4</t>
-        </is>
-      </c>
-      <c r="J15" t="n">
-        <v>1</v>
-      </c>
+          <t>70 kV</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>IBT 150/70 kV</t>
+          <t>KTT Aspek 40 MVA</t>
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
@@ -1574,33 +1566,51 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Semen Baru (bus 70 kV)</t>
+          <t>IBT 150/70 kV Semen Baru</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
+          <t>IBT 1 SMNRU</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>IBT 3-Winding</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>150/70 kV</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>SMNRU</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
           <t>SMNRU4</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Busbar GI</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>2</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>70 kV</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>IBT 150/70 kV</t>
+        </is>
+      </c>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
@@ -1631,12 +1641,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Semen Mas</t>
+          <t>Semen Baru (bus 70 kV)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SMNMA</t>
+          <t>SMNRU4</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1645,7 +1655,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1657,11 +1667,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>KTT Sucofindo 40 MVA</t>
-        </is>
-      </c>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
@@ -1692,12 +1698,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Gandaria</t>
+          <t>Semen Mas</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>GDRIA</t>
+          <t>SMNMA</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1706,11 +1712,11 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>150 kV</t>
+          <t>70 kV</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -1720,7 +1726,7 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>aset milik KTT</t>
+          <t>KTT Sucofindo 40 MVA</t>
         </is>
       </c>
       <c r="M18" t="inlineStr"/>
@@ -1753,12 +1759,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Salak</t>
+          <t>Gandaria</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SALAK</t>
+          <t>GDRIA</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1767,7 +1773,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1779,7 +1785,11 @@
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>aset milik KTT</t>
+        </is>
+      </c>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
@@ -1800,7 +1810,7 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>SALAK</t>
+          <t>CIBINONG</t>
         </is>
       </c>
     </row>
@@ -1810,17 +1820,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Salak Baru (GIS)</t>
+          <t>Salak</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>SLBRU</t>
+          <t>SALAK</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Busbar GIS</t>
+          <t>Busbar GI</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -1836,11 +1846,7 @@
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>T/L bay single phi arah Bogor Baru &amp; Cibadak Baru</t>
-        </is>
-      </c>
+      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
@@ -1850,14 +1856,10 @@
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -1875,17 +1877,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Pelabuhan Ratu</t>
+          <t>Salak Baru (GIS)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>PRATU</t>
+          <t>SLBRU</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Busbar GI</t>
+          <t>Busbar GIS</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -1901,7 +1903,11 @@
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>T/L bay single phi arah Bogor Baru &amp; Cibadak Baru</t>
+        </is>
+      </c>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
@@ -1916,7 +1922,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -1936,12 +1942,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Cibadak Baru</t>
+          <t>Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CBDRU</t>
+          <t>PRATU</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1950,7 +1956,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1997,12 +2003,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Bayah</t>
+          <t>Cibadak Baru</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>BAYAH</t>
+          <t>CBDRU</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2023,11 +2029,7 @@
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>KTT Cemindo 70 MVA</t>
-        </is>
-      </c>
+      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
@@ -2037,10 +2039,14 @@
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="R23" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -2058,12 +2064,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Semen Jawa</t>
+          <t>Bayah</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>SJAWA</t>
+          <t>BAYAH</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2084,7 +2090,11 @@
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>KTT Cemindo 70 MVA</t>
+        </is>
+      </c>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
@@ -2094,14 +2104,10 @@
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -2119,12 +2125,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Ciawi</t>
+          <t>Semen Jawa</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CIAWI</t>
+          <t>SJAWA</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2155,10 +2161,14 @@
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="R25" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -2176,12 +2186,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Lembur Situ</t>
+          <t>Ciawi</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>LBSTU</t>
+          <t>CIAWI</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2190,7 +2200,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2212,14 +2222,10 @@
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -2237,12 +2243,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Jampang</t>
+          <t>Lembur Situ</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>JMPNG</t>
+          <t>LBSTU</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2251,7 +2257,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2273,10 +2279,14 @@
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="R27" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -2294,12 +2304,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Mangunreja/Mping</t>
+          <t>Jampang</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>MPING</t>
+          <t>JMPNG</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2351,51 +2361,33 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>IBT 150/70 kV Cibadak</t>
+          <t>Mangunreja/Mping</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>IBT 1 CBDRU</t>
+          <t>MPING</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>IBT 3-Winding</t>
+          <t>Busbar GI</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>150/70 kV</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>CBDRU</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>CBDK4</t>
-        </is>
-      </c>
-      <c r="J29" t="n">
-        <v>1</v>
-      </c>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>IBT 150/70 kV</t>
-        </is>
-      </c>
+      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
@@ -2426,33 +2418,51 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Cibadak (bus 70 kV)</t>
+          <t>IBT 150/70 kV Cibadak</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
+          <t>IBT 1 CBDRU</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>IBT 3-Winding</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>2</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>150/70 kV</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>CBDRU</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
           <t>CBDK4</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Busbar GI</t>
-        </is>
-      </c>
-      <c r="E30" t="n">
-        <v>2</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>70 kV</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+      <c r="J30" t="n">
+        <v>1</v>
+      </c>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>IBT 150/70 kV</t>
+        </is>
+      </c>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
@@ -2483,12 +2493,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Ubrug</t>
+          <t>Cibadak (bus 70 kV)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>UBRUG</t>
+          <t>CBDK4</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2540,12 +2550,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Pelabuhan Ratu (bus 70 kV)</t>
+          <t>Ubrug</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>PRATU4</t>
+          <t>UBRUG</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2554,7 +2564,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2597,12 +2607,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Bogor Baru</t>
+          <t>Pelabuhan Ratu (bus 70 kV)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>BGBRU</t>
+          <t>PRATU4</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2611,11 +2621,11 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>150 kV</t>
+          <t>70 kV</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
@@ -2623,11 +2633,7 @@
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>GI simpul; trafo &gt;70%</t>
-        </is>
-      </c>
+      <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
@@ -2637,14 +2643,10 @@
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>1;6</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -2652,7 +2654,7 @@
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>CIBINONG;SALAK</t>
+          <t>SALAK</t>
         </is>
       </c>
     </row>
@@ -2662,12 +2664,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Sentul</t>
+          <t>Bogor Baru</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>SNTUL</t>
+          <t>BGBRU</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2688,7 +2690,11 @@
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>GI simpul; trafo &gt;70%</t>
+        </is>
+      </c>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
@@ -2703,7 +2709,7 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1;6</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -2723,12 +2729,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Katulampa</t>
+          <t>Sentul</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>KTLPA</t>
+          <t>SNTUL</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2737,7 +2743,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2764,7 +2770,7 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -2784,21 +2790,21 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>PLTP Salak Lama unit 1,2,3</t>
+          <t>Katulampa</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>KIT_SALAK</t>
+          <t>KTLPA</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Pembangkit</t>
+          <t>Busbar GI</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2820,10 +2826,14 @@
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="R36" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -2831,7 +2841,7 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>SALAK</t>
+          <t>CIBINONG;SALAK</t>
         </is>
       </c>
     </row>
@@ -2841,12 +2851,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>PLTP Salak Lama unit Binary</t>
+          <t>PLTP Salak Lama unit 1,2,3</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>KIT_SALAKB</t>
+          <t>KIT_SALAK</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2898,12 +2908,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>PLTP Salak Baru unit 4,5,6</t>
+          <t>PLTP Salak Lama unit Binary</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>KIT_SLBRU</t>
+          <t>KIT_SALAKB</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2955,12 +2965,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>PLTU Pelabuhan Ratu unit 1,2,3</t>
+          <t>PLTP Salak Baru unit 4,5,6</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>KIT_PRATU</t>
+          <t>KIT_SLBRU</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -3012,12 +3022,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>PLTA Ubrug unit 1,2,3</t>
+          <t>PLTU Pelabuhan Ratu unit 1,2,3</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>KIT_UBRUG</t>
+          <t>KIT_PRATU</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3026,11 +3036,11 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>70 kV</t>
+          <t>150 kV</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
@@ -3069,25 +3079,25 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Cianjur/Cugenang (UP2B Jabar)</t>
+          <t>PLTA Ubrug unit 1,2,3</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CGRLG</t>
+          <t>KIT_UBRUG</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Busbar GI</t>
+          <t>Pembangkit</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>150 kV</t>
+          <t>70 kV</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
@@ -3095,22 +3105,14 @@
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>UP2B 2 (JABAR): CNJUR : - / CGRLG : Trf 9,10</t>
-        </is>
-      </c>
+      <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>SOURCE_BOUNDARY</t>
-        </is>
-      </c>
+      <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Normal</t>
@@ -3134,12 +3136,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Lengkong Dar (UP2B Jabar)</t>
+          <t>Cianjur/Cugenang (UP2B Jabar)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>LGDAR</t>
+          <t>CGRLG</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -3162,7 +3164,7 @@
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
-          <t>UP2B 2 (JABAR): LGDAR Trf 1,2,3,4</t>
+          <t>UP2B 2 (JABAR): CNJUR : - / CGRLG : Trf 9,10</t>
         </is>
       </c>
       <c r="M42" t="inlineStr"/>
@@ -3188,6 +3190,71 @@
         </is>
       </c>
       <c r="S42" t="inlineStr">
+        <is>
+          <t>SALAK</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Lengkong Dar (UP2B Jabar)</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>LGDAR</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Busbar GI</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>3</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>UP2B 2 (JABAR): LGDAR Trf 1,2,3,4</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>SOURCE_BOUNDARY</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>Jawa Barat</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
         <is>
           <t>SALAK</t>
         </is>
